--- a/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
+++ b/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
@@ -3228,11 +3228,7 @@
     </row>
     <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
@@ -3248,17 +3244,9 @@
         </is>
       </c>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="24"/>
     </row>
     <row r="7" ht="91.25" customHeight="true">
@@ -3302,36 +3290,25 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C8" s="23"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="23"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K8" s="23"/>
@@ -3375,8 +3352,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="24"/>
@@ -3396,15 +3372,13 @@
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="24"/>
@@ -3446,17 +3420,9 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F12" s="21"/>
       <c r="G12" s="23"/>
       <c r="H12" s="21"/>
       <c r="I12" s="23"/>
@@ -3513,16 +3479,14 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
+++ b/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
@@ -3352,7 +3352,8 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="C10" s="24"/>
@@ -3372,13 +3373,15 @@
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="K10" s="24"/>

--- a/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
+++ b/sheets/조재수대금교본/검수/아내에게 바치는 노래.xlsx
@@ -3098,15 +3098,15 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
